--- a/app/data/exports/需要予測_20260707.xlsx
+++ b/app/data/exports/需要予測_20260707.xlsx
@@ -439,7 +439,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>需要予測（部品別・月別数量） — 実行: 2026-07-07T06:35:59.934599 / 手法: sku-selected-v3</t>
+          <t>需要予測（部品別・月別数量） — 実行: 2026-07-07T07:34:40.549843 / 手法: sku-selected-v3</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
@@ -465,7 +465,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>出力日時: 2026-07-07 15:44 — 検証WAPEは各SKUの直近6か月ホールドアウトによる（低いほど良い）</t>
+          <t>出力日時: 2026-07-07 17:44 — 検証WAPEは各SKUの直近6か月ホールドアウトによる（低いほど良い）</t>
         </is>
       </c>
     </row>
@@ -5889,12 +5889,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>MAG CORELIQUID E360 黒</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>グラフィックカード</t>
+          <t>ファンS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5902,196 +5902,199 @@
           <t>flat3</t>
         </is>
       </c>
+      <c r="D85" t="n">
+        <v>32.6</v>
+      </c>
       <c r="E85" t="n">
-        <v>7970.920589585974</v>
+        <v>5066.960627992638</v>
       </c>
       <c r="F85" t="n">
-        <v>13756</v>
+        <v>13804</v>
       </c>
       <c r="G85" t="n">
-        <v>1780</v>
+        <v>2304</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="J85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="K85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="L85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="M85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="N85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="O85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="P85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="Q85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="R85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="S85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
       <c r="T85" t="n">
-        <v>1146.3</v>
+        <v>1150.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>M9020</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ﾏｳｽN</t>
+          <t>グラフィックカード</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>trend</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>107</v>
+          <t>flat3</t>
+        </is>
       </c>
       <c r="E86" t="n">
-        <v>20770.73373112589</v>
+        <v>7970.920589585974</v>
       </c>
       <c r="F86" t="n">
-        <v>13641</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>13756</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1780</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1431.9</v>
+        <v>1146.3</v>
       </c>
       <c r="J86" t="n">
-        <v>1337.5</v>
+        <v>1146.3</v>
       </c>
       <c r="K86" t="n">
-        <v>1262.2</v>
+        <v>1146.3</v>
       </c>
       <c r="L86" t="n">
-        <v>1201.6</v>
+        <v>1146.3</v>
       </c>
       <c r="M86" t="n">
-        <v>1152.3</v>
+        <v>1146.3</v>
       </c>
       <c r="N86" t="n">
-        <v>1112</v>
+        <v>1146.3</v>
       </c>
       <c r="O86" t="n">
-        <v>1078.9</v>
+        <v>1146.3</v>
       </c>
       <c r="P86" t="n">
-        <v>1051.5</v>
+        <v>1146.3</v>
       </c>
       <c r="Q86" t="n">
-        <v>1028.8</v>
+        <v>1146.3</v>
       </c>
       <c r="R86" t="n">
-        <v>1009.8</v>
+        <v>1146.3</v>
       </c>
       <c r="S86" t="n">
-        <v>994</v>
+        <v>1146.3</v>
       </c>
       <c r="T86" t="n">
-        <v>980.8</v>
+        <v>1146.3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>U5-225</t>
+          <t>M9020</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>ﾏｳｽN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>flat3</t>
-        </is>
+          <t>trend</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>107</v>
       </c>
       <c r="E87" t="n">
-        <v>-187.2857142857145</v>
+        <v>20770.73373112589</v>
       </c>
       <c r="F87" t="n">
-        <v>13579</v>
-      </c>
-      <c r="G87" t="n">
-        <v>2450.5</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
+        <v>13641</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>1131.6</v>
+        <v>1431.9</v>
       </c>
       <c r="J87" t="n">
-        <v>1131.6</v>
+        <v>1337.5</v>
       </c>
       <c r="K87" t="n">
-        <v>1131.6</v>
+        <v>1262.2</v>
       </c>
       <c r="L87" t="n">
-        <v>1131.6</v>
+        <v>1201.6</v>
       </c>
       <c r="M87" t="n">
-        <v>1131.6</v>
+        <v>1152.3</v>
       </c>
       <c r="N87" t="n">
-        <v>1131.6</v>
+        <v>1112</v>
       </c>
       <c r="O87" t="n">
-        <v>1131.6</v>
+        <v>1078.9</v>
       </c>
       <c r="P87" t="n">
-        <v>1131.6</v>
+        <v>1051.5</v>
       </c>
       <c r="Q87" t="n">
-        <v>1131.6</v>
+        <v>1028.8</v>
       </c>
       <c r="R87" t="n">
-        <v>1131.6</v>
+        <v>1009.8</v>
       </c>
       <c r="S87" t="n">
-        <v>1131.6</v>
+        <v>994</v>
       </c>
       <c r="T87" t="n">
-        <v>1131.6</v>
+        <v>980.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MAG CORELIQUID E360 黒</t>
+          <t>U5-225</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ファンS</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6099,17 +6102,14 @@
           <t>flat3</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>32.6</v>
-      </c>
       <c r="E88" t="n">
-        <v>5066.960627992638</v>
+        <v>-187.2857142857145</v>
       </c>
       <c r="F88" t="n">
-        <v>13556</v>
+        <v>13579</v>
       </c>
       <c r="G88" t="n">
-        <v>1920</v>
+        <v>2450.5</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -6117,40 +6117,40 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
       <c r="J88" t="n">
-        <v>903</v>
+        <v>1131.6</v>
       </c>
       <c r="K88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
       <c r="L88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
       <c r="M88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
       <c r="N88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
       <c r="O88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
       <c r="P88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
       <c r="Q88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
       <c r="R88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
       <c r="S88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
       <c r="T88" t="n">
-        <v>1150.3</v>
+        <v>1131.6</v>
       </c>
     </row>
     <row r="89">
@@ -7521,30 +7521,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A520M</t>
+          <t>636S-M2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ﾏｻﾞｰﾎﾞｰﾄﾞ</t>
+          <t>ファンS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>trend</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>276.2</v>
+          <t>flat3</t>
+        </is>
       </c>
       <c r="E111" t="n">
-        <v>1484.97573491556</v>
+        <v>160.1720430107527</v>
       </c>
       <c r="F111" t="n">
-        <v>8699</v>
+        <v>8992</v>
       </c>
       <c r="G111" t="n">
-        <v>1500</v>
+        <v>3086.8</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7552,111 +7549,121 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>502.2</v>
+        <v>749.3</v>
       </c>
       <c r="J111" t="n">
-        <v>555.6</v>
+        <v>749.3</v>
       </c>
       <c r="K111" t="n">
-        <v>605.4</v>
+        <v>749.3</v>
       </c>
       <c r="L111" t="n">
-        <v>651.2</v>
+        <v>749.3</v>
       </c>
       <c r="M111" t="n">
-        <v>692.8</v>
+        <v>749.3</v>
       </c>
       <c r="N111" t="n">
-        <v>730.3</v>
+        <v>749.3</v>
       </c>
       <c r="O111" t="n">
-        <v>763.8</v>
+        <v>749.3</v>
       </c>
       <c r="P111" t="n">
-        <v>793.4</v>
+        <v>749.3</v>
       </c>
       <c r="Q111" t="n">
-        <v>819.6</v>
+        <v>749.3</v>
       </c>
       <c r="R111" t="n">
-        <v>842.4</v>
+        <v>749.3</v>
       </c>
       <c r="S111" t="n">
-        <v>862.4</v>
+        <v>749.3</v>
       </c>
       <c r="T111" t="n">
-        <v>879.7</v>
+        <v>749.3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>金具　Gemini (Dark gray)</t>
+          <t>A520M</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ｻﾌﾟﾗｲ用品N</t>
+          <t>ﾏｻﾞｰﾎﾞｰﾄﾞ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>flat3</t>
-        </is>
+          <t>trend</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>276.2</v>
       </c>
       <c r="E112" t="n">
-        <v>12459.8786995297</v>
+        <v>1484.97573491556</v>
       </c>
       <c r="F112" t="n">
-        <v>8582</v>
-      </c>
-      <c r="H112" t="inlineStr"/>
+        <v>8699</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>715.2</v>
+        <v>502.2</v>
       </c>
       <c r="J112" t="n">
-        <v>715.2</v>
+        <v>555.6</v>
       </c>
       <c r="K112" t="n">
-        <v>715.2</v>
+        <v>605.4</v>
       </c>
       <c r="L112" t="n">
-        <v>715.2</v>
+        <v>651.2</v>
       </c>
       <c r="M112" t="n">
-        <v>715.2</v>
+        <v>692.8</v>
       </c>
       <c r="N112" t="n">
-        <v>715.2</v>
+        <v>730.3</v>
       </c>
       <c r="O112" t="n">
-        <v>715.2</v>
+        <v>763.8</v>
       </c>
       <c r="P112" t="n">
-        <v>715.2</v>
+        <v>793.4</v>
       </c>
       <c r="Q112" t="n">
-        <v>715.2</v>
+        <v>819.6</v>
       </c>
       <c r="R112" t="n">
-        <v>715.2</v>
+        <v>842.4</v>
       </c>
       <c r="S112" t="n">
-        <v>715.2</v>
+        <v>862.4</v>
       </c>
       <c r="T112" t="n">
-        <v>715.2</v>
+        <v>879.7</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FKE4_152 AMD</t>
+          <t>金具　Gemini (Dark gray)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ファンN</t>
+          <t>ｻﾌﾟﾗｲ用品N</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7665,65 +7672,58 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2955</v>
+        <v>12459.8786995297</v>
       </c>
       <c r="F113" t="n">
-        <v>8568</v>
-      </c>
-      <c r="G113" t="n">
-        <v>900.6</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
+        <v>8582</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="J113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="K113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="L113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="M113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="N113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="O113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="P113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="Q113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="R113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="S113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
       <c r="T113" t="n">
-        <v>714</v>
+        <v>715.2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>636S-M2</t>
+          <t>FKE4_152 AMD</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ファンS</t>
+          <t>ファンN</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7732,13 +7732,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>160.1720430107527</v>
+        <v>2955</v>
       </c>
       <c r="F114" t="n">
-        <v>8442</v>
+        <v>8568</v>
       </c>
       <c r="G114" t="n">
-        <v>2384.9</v>
+        <v>900.6</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7746,40 +7746,40 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>200</v>
+        <v>714</v>
       </c>
       <c r="J114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
       <c r="K114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
       <c r="L114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
       <c r="M114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
       <c r="N114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
       <c r="O114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
       <c r="P114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
       <c r="Q114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
       <c r="R114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
       <c r="S114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
       <c r="T114" t="n">
-        <v>749.3</v>
+        <v>714</v>
       </c>
     </row>
     <row r="115">
@@ -10593,207 +10593,214 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MAG CORELIQUID E360 白</t>
+          <t>SD5-32G48</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ファンS</t>
+          <t>メモリ</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>flat3</t>
-        </is>
+          <t>seasonal</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>127.9</v>
       </c>
       <c r="E156" t="n">
-        <v>7738.243332453167</v>
+        <v>4679</v>
       </c>
       <c r="F156" t="n">
-        <v>4998</v>
-      </c>
-      <c r="H156" t="inlineStr"/>
+        <v>4895</v>
+      </c>
+      <c r="G156" t="n">
+        <v>550</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>387.3</v>
+        <v>396.8</v>
       </c>
       <c r="J156" t="n">
-        <v>387.3</v>
+        <v>459.2</v>
       </c>
       <c r="K156" t="n">
-        <v>738</v>
+        <v>516</v>
       </c>
       <c r="L156" t="n">
-        <v>387.3</v>
+        <v>400.2</v>
       </c>
       <c r="M156" t="n">
-        <v>387.3</v>
+        <v>472.5</v>
       </c>
       <c r="N156" t="n">
-        <v>387.3</v>
+        <v>631.8</v>
       </c>
       <c r="O156" t="n">
-        <v>387.3</v>
+        <v>472.2</v>
       </c>
       <c r="P156" t="n">
-        <v>387.3</v>
+        <v>250.5</v>
       </c>
       <c r="Q156" t="n">
-        <v>387.3</v>
+        <v>389.4</v>
       </c>
       <c r="R156" t="n">
-        <v>387.3</v>
+        <v>414.3</v>
       </c>
       <c r="S156" t="n">
-        <v>387.3</v>
+        <v>215</v>
       </c>
       <c r="T156" t="n">
-        <v>387.3</v>
+        <v>276.8</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SD5-32G48</t>
+          <t>ry77800X3D</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>メモリ</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>seasonal</t>
+          <t>median6</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>127.9</v>
+        <v>58.5</v>
       </c>
       <c r="E157" t="n">
-        <v>4679</v>
+        <v>452</v>
       </c>
       <c r="F157" t="n">
-        <v>4895</v>
+        <v>4884</v>
       </c>
       <c r="G157" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>396.8</v>
+        <v>407</v>
       </c>
       <c r="J157" t="n">
-        <v>459.2</v>
+        <v>407</v>
       </c>
       <c r="K157" t="n">
-        <v>516</v>
+        <v>407</v>
       </c>
       <c r="L157" t="n">
-        <v>400.2</v>
+        <v>407</v>
       </c>
       <c r="M157" t="n">
-        <v>472.5</v>
+        <v>407</v>
       </c>
       <c r="N157" t="n">
-        <v>631.8</v>
+        <v>407</v>
       </c>
       <c r="O157" t="n">
-        <v>472.2</v>
+        <v>407</v>
       </c>
       <c r="P157" t="n">
-        <v>250.5</v>
+        <v>407</v>
       </c>
       <c r="Q157" t="n">
-        <v>389.4</v>
+        <v>407</v>
       </c>
       <c r="R157" t="n">
-        <v>414.3</v>
+        <v>407</v>
       </c>
       <c r="S157" t="n">
-        <v>215</v>
+        <v>407</v>
       </c>
       <c r="T157" t="n">
-        <v>276.8</v>
+        <v>407</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ry77800X3D</t>
+          <t>SR-CBUB-002B</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>PC DIYｻﾌﾟﾗｲ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>median6</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>58.5</v>
+          <t>flat3</t>
+        </is>
       </c>
       <c r="E158" t="n">
-        <v>452</v>
+        <v>1338.02350250071</v>
       </c>
       <c r="F158" t="n">
-        <v>4884</v>
+        <v>4772</v>
       </c>
       <c r="G158" t="n">
-        <v>552</v>
+        <v>650.5</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="J158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="K158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="L158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="M158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="N158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="O158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="P158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="Q158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="R158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="S158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
       <c r="T158" t="n">
-        <v>407</v>
+        <v>397.7</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SR-CBUB-002B</t>
+          <t>MSI GALLERIAロゴシール(E240/E360)黒</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10807,65 +10814,65 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1338.02350250071</v>
+        <v>2347.012265019771</v>
       </c>
       <c r="F159" t="n">
-        <v>4772</v>
+        <v>4652</v>
       </c>
       <c r="G159" t="n">
-        <v>650.5</v>
+        <v>512</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="J159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="K159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="L159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="M159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="N159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="O159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="P159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="Q159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="R159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="S159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
       <c r="T159" t="n">
-        <v>397.7</v>
+        <v>387.7</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MSI GALLERIAロゴシール(E240/E360)黒</t>
+          <t>MAG CORELIQUID E360 白</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PC DIYｻﾌﾟﾗｲ</t>
+          <t>ファンS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10874,54 +10881,47 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2347.012265019771</v>
+        <v>7738.243332453167</v>
       </c>
       <c r="F160" t="n">
-        <v>4652</v>
-      </c>
-      <c r="G160" t="n">
-        <v>512</v>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
+        <v>4648</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="J160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="K160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="L160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="M160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="N160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="O160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="P160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="Q160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="R160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="S160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
       <c r="T160" t="n">
-        <v>387.7</v>
+        <v>387.3</v>
       </c>
     </row>
     <row r="161">
@@ -16571,30 +16571,30 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>CLE-L24-258V-UMA-32G-L7 Thirdwave</t>
+          <t>X870E</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ノートベア</t>
+          <t>ﾏｻﾞｰﾎﾞｰﾄﾞ</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>flat6</t>
+          <t>median6</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>54.5</v>
+        <v>52.6</v>
       </c>
       <c r="E247" t="n">
-        <v>-104.8494623655914</v>
+        <v>464.156989247312</v>
       </c>
       <c r="F247" t="n">
-        <v>1844</v>
+        <v>1854</v>
       </c>
       <c r="G247" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -16602,69 +16602,69 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="J247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="K247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="L247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="M247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="N247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="O247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="P247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="Q247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="R247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="S247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
       <c r="T247" t="n">
-        <v>153.7</v>
+        <v>154.5</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>U7-265KF</t>
+          <t>CLE-L24-258V-UMA-32G-L7 Thirdwave</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>ノートベア</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>median6</t>
+          <t>flat6</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>93.8</v>
+        <v>54.5</v>
       </c>
       <c r="E248" t="n">
-        <v>52.71428571428577</v>
+        <v>-104.8494623655914</v>
       </c>
       <c r="F248" t="n">
-        <v>1824</v>
+        <v>1844</v>
       </c>
       <c r="G248" t="n">
-        <v>251.3</v>
+        <v>1000</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -16672,51 +16672,51 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="J248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="K248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="L248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="M248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="N248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="O248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="P248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="Q248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="R248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="S248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
       <c r="T248" t="n">
-        <v>152</v>
+        <v>153.7</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>X870E</t>
+          <t>U7-265KF</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ﾏｻﾞｰﾎﾞｰﾄﾞ</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -16725,16 +16725,16 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>52.6</v>
+        <v>93.8</v>
       </c>
       <c r="E249" t="n">
-        <v>464.156989247312</v>
+        <v>52.71428571428577</v>
       </c>
       <c r="F249" t="n">
-        <v>1778</v>
+        <v>1824</v>
       </c>
       <c r="G249" t="n">
-        <v>250</v>
+        <v>251.3</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -16742,40 +16742,40 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="J249" t="n">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="K249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="L249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="M249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="N249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="O249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="P249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="Q249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="R249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="S249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="T249" t="n">
-        <v>154.5</v>
+        <v>152</v>
       </c>
     </row>
     <row r="250">
